--- a/content/xls/indicators_01.01.2026.xlsx
+++ b/content/xls/indicators_01.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D26CB2-53CD-40B9-9CEC-1D6771E31487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCCEADD-887A-4D99-A1B4-A8308824FEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3397" yWindow="3397" windowWidth="23631" windowHeight="12541" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10511" yWindow="2117" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">3.1 п.п. </t>
+      <t xml:space="preserve">2 ед. </t>
     </r>
     <r>
       <rPr>
@@ -86,277 +86,6 @@
       </rPr>
       <t>к 01.07.2025</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>↓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 2.6 п.п. к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>↑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">точ. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">3 ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">2 ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">7 ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">2 ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">35 чел. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <t>81.9%</t>
-  </si>
-  <si>
-    <t>18.1%</t>
-  </si>
-  <si>
-    <t>200 точек</t>
-  </si>
-  <si>
-    <t>500 ед.</t>
-  </si>
-  <si>
-    <t>300 ед.</t>
-  </si>
-  <si>
-    <t>200 ед.</t>
-  </si>
-  <si>
-    <t>10 ед.</t>
-  </si>
-  <si>
-    <t>40 чел.</t>
   </si>
   <si>
     <t>Уровень потребности в развитии 
@@ -373,26 +102,351 @@
   </si>
   <si>
     <t>Присутствие финансовых помощников</t>
+  </si>
+  <si>
+    <t>80.5%</t>
+  </si>
+  <si>
+    <t>17.0%</t>
+  </si>
+  <si>
+    <t>217 точек</t>
+  </si>
+  <si>
+    <t>555 ед.</t>
+  </si>
+  <si>
+    <t>377 ед.</t>
+  </si>
+  <si>
+    <t>216 ед.</t>
+  </si>
+  <si>
+    <t>4 ед.</t>
+  </si>
+  <si>
+    <t>35 чел.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> п.п. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 0.5 п.п. к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">точ. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">чел. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -490,26 +544,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -810,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -819,16 +870,16 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -838,54 +889,54 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="H3" s="7" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">

--- a/content/xls/indicators_01.01.2026.xlsx
+++ b/content/xls/indicators_01.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCCEADD-887A-4D99-A1B4-A8308824FEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0390F4-1221-4ABE-81F6-8E4621FF69AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10511" yWindow="2117" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,6 @@
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Присутствие банков</t>
-  </si>
-  <si>
-    <t>Присутствие Отделений почтовой связи</t>
-  </si>
-  <si>
     <t>↑</t>
   </si>
   <si>
@@ -92,18 +86,6 @@
 дистанционного банковского обслуживания</t>
   </si>
   <si>
-    <t>Присутствие банкоматов</t>
-  </si>
-  <si>
-    <t>Присутствие торговых точек с сервисом «Выдача наличных на кассе»</t>
-  </si>
-  <si>
-    <t>Присутствие точек финансового доступа</t>
-  </si>
-  <si>
-    <t>Присутствие финансовых помощников</t>
-  </si>
-  <si>
     <t>80.5%</t>
   </si>
   <si>
@@ -435,18 +417,44 @@
       </rPr>
       <t>к 01.07.2025</t>
     </r>
+  </si>
+  <si>
+    <t>Количество банков</t>
+  </si>
+  <si>
+    <t>Количество Отделений почтовой связи</t>
+  </si>
+  <si>
+    <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Количество торговых точек с сервисом «Выдача наличных на кассе»</t>
+  </si>
+  <si>
+    <t>Количество точек финансового доступа</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -549,18 +557,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -861,25 +869,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -889,69 +897,69 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/content/xls/indicators_01.01.2026.xlsx
+++ b/content/xls/indicators_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0390F4-1221-4ABE-81F6-8E4621FF69AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97284A4B-69AB-40F4-8A3F-71D88E3495C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>80.5%</t>
   </si>
   <si>
-    <t>17.0%</t>
-  </si>
-  <si>
     <t>217 точек</t>
   </si>
   <si>
@@ -435,6 +432,9 @@
   </si>
   <si>
     <t>Количество финансовых помощников</t>
+  </si>
+  <si>
+    <t>16.6%</t>
   </si>
 </sst>
 </file>
@@ -872,22 +872,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -900,51 +900,51 @@
         <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">

--- a/content/xls/indicators_01.01.2026.xlsx
+++ b/content/xls/indicators_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97284A4B-69AB-40F4-8A3F-71D88E3495C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D020BD1A-12F4-40D6-8F3F-40F290E6B651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,260 +181,260 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve"> 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">точ. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">чел. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.07.2025</t>
+    </r>
+  </si>
+  <si>
+    <t>Количество банков</t>
+  </si>
+  <si>
+    <t>Количество Отделений почтовой связи</t>
+  </si>
+  <si>
+    <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Количество торговых точек с сервисом «Выдача наличных на кассе»</t>
+  </si>
+  <si>
+    <t>Количество точек финансового доступа</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
+  </si>
+  <si>
+    <t>16.6%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> 0.5 п.п. к 01.07.2025</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>↑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">точ. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>↓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">чел. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
-    <t>Количество банков</t>
-  </si>
-  <si>
-    <t>Количество Отделений почтовой связи</t>
-  </si>
-  <si>
-    <t>Количество банкоматов</t>
-  </si>
-  <si>
-    <t>Количество торговых точек с сервисом «Выдача наличных на кассе»</t>
-  </si>
-  <si>
-    <t>Количество точек финансового доступа</t>
-  </si>
-  <si>
-    <t>Количество финансовых помощников</t>
-  </si>
-  <si>
-    <t>16.6%</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -569,6 +569,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -872,22 +875,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -900,7 +903,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
@@ -925,26 +928,26 @@
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">

--- a/content/xls/indicators_01.01.2026.xlsx
+++ b/content/xls/indicators_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D020BD1A-12F4-40D6-8F3F-40F290E6B651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D1F931-3110-4358-924A-3E37C71F9D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
 дистанционного банковского обслуживания</t>
   </si>
   <si>
-    <t>80.5%</t>
-  </si>
-  <si>
     <t>217 точек</t>
   </si>
   <si>
@@ -435,6 +432,10 @@
       </rPr>
       <t xml:space="preserve"> 0.5 п.п. к 01.07.2025</t>
     </r>
+  </si>
+  <si>
+    <t>80.5%
+Выше среднего</t>
   </si>
 </sst>
 </file>
@@ -552,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -573,6 +574,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -875,22 +879,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -898,56 +902,56 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:13" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">

--- a/content/xls/indicators_01.01.2026.xlsx
+++ b/content/xls/indicators_01.01.2026.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Юлия\Desktop\ФД_2026\10.08.26\от Егора_итоговые файлы_25.08.26\Ответ_измен. ур.дбо_зеленым\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D1F931-3110-4358-924A-3E37C71F9D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4908C9D-E4AF-4BCF-9D77-8F078273EFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -411,31 +402,31 @@
     <t>16.6%</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>↑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 0.5 п.п. к 01.07.2025</t>
-    </r>
-  </si>
-  <si>
     <t>80.5%
 Выше среднего</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 0.5 п.п. к 01.07.2025</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -859,19 +850,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="31.109375" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" customWidth="1"/>
-    <col min="8" max="8" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="59.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="59.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -902,9 +893,9 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>24</v>
@@ -928,12 +919,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>13</v>
@@ -954,17 +945,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
